--- a/Employee_Reports_wi52/Jason Puzon Dy Q0501.xlsx
+++ b/Employee_Reports_wi52/Jason Puzon Dy Q0501.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-93</v>
+        <v>-101</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-118</v>
+        <v>-126</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-82</v>
+        <v>-90</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>-83</v>
+        <v>-91</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -744,20 +744,20 @@
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>05-Oct-2025</t>
+          <t>25-Aug-2026</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>05-Oct-2027</t>
+          <t>24-Aug-2028</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>411</v>
+        <v>727</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -790,11 +790,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
